--- a/data/polling_place_list/data (1).xlsx
+++ b/data/polling_place_list/data (1).xlsx
@@ -788,19 +788,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>34.34378062</v>
+        <v>34.34409509</v>
       </c>
       <c r="C13" t="str">
-        <v>134.0558113</v>
+        <v>134.0565220</v>
       </c>
       <c r="D13" t="str">
         <v>第12投票区</v>
       </c>
       <c r="E13" t="str">
-        <v>旧新塩屋町小学校体育館</v>
+        <v>高松市総合教育センター（多目的洋室）</v>
       </c>
       <c r="F13" t="str">
-        <v>キュウシンシオヤマチショウガッコウタイイクカン</v>
+        <v>タカマツシソウゴウキョウイクセンター（タモクテキヨウシツ）</v>
       </c>
       <c r="G13" t="str">
         <v>香川県高松市末広町5</v>
@@ -1076,22 +1076,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>34.32577618</v>
+        <v>34.328708434</v>
       </c>
       <c r="C22" t="str">
-        <v>134.0913691</v>
+        <v>134.0869970</v>
       </c>
       <c r="D22" t="str">
         <v>第21投票区</v>
       </c>
       <c r="E22" t="str">
-        <v>旧春日幼稚園</v>
+        <v>高松大学・高松短期大学学生会館</v>
       </c>
       <c r="F22" t="str">
-        <v>キュウカスガヨウチエン</v>
+        <v>タカマツダイガク・タカマツタンキダイガクガクセイカイカン</v>
       </c>
       <c r="G22" t="str">
-        <v>香川県高松市春日町744</v>
+        <v>香川県高松市春日町960</v>
       </c>
       <c r="H22" t="str">
         <v>香川県第１区</v>
@@ -1428,22 +1428,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>34.28638923532128</v>
+        <v>34.27988468</v>
       </c>
       <c r="C33" t="str">
-        <v>134.02356112267915</v>
+        <v>134.0224567</v>
       </c>
       <c r="D33" t="str">
         <v>第32投票区</v>
       </c>
       <c r="E33" t="str">
-        <v>高松南高校校舎棟西館</v>
+        <v>らく楽寺井幼稚園</v>
       </c>
       <c r="F33" t="str">
-        <v>タカマツミナミコウコウコウシャトウニシカン</v>
+        <v>ラクラクテライヨウチエン</v>
       </c>
       <c r="G33" t="str">
-        <v>香川県高松市一宮町531</v>
+        <v>香川県高松市寺井町1369</v>
       </c>
       <c r="H33" t="str">
         <v>香川県第１区</v>
@@ -1460,22 +1460,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>34.26746144</v>
+        <v>34.26944320</v>
       </c>
       <c r="C34" t="str">
-        <v>134.0064324</v>
+        <v>134.0100840</v>
       </c>
       <c r="D34" t="str">
         <v>第33投票区</v>
       </c>
       <c r="E34" t="str">
-        <v>川岡小学校体育館</v>
+        <v>川岡コミュニティセンター</v>
       </c>
       <c r="F34" t="str">
-        <v>カワオカショウガッコウタイイクカン</v>
+        <v>カワオカコミュニティセンター</v>
       </c>
       <c r="G34" t="str">
-        <v>香川県高松市川部町1552</v>
+        <v>香川県高松市川部町486-3</v>
       </c>
       <c r="H34" t="str">
         <v>香川県第１区</v>
